--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,2071 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129637210</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>466935</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6875038</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129634992</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>467124</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6874859</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129635001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79634</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>467127</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6874858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129635902</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6874896</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129636078</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92835</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>466993</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6874968</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129637076</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78710</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466947</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6875014</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129634476</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467118</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6874875</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129635881</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467091</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6874896</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129635733</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79634</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467154</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6874829</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129637051</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78710</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466957</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6875023</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129635736</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>467160</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6874835</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129636144</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>467000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6874978</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129634638</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>467109</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6874851</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129634628</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>467109</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6874851</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129637336</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79634</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466937</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6875120</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129635730</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>467158</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6874824</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129637233</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79634</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>466914</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6875058</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129635973</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78710</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>467044</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6874932</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129635621</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78710</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>353</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6874854</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129635917</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467081</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6874889</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129636001</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92835</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467033</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6874940</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129634992</v>
+        <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467124</v>
+        <v>467127</v>
       </c>
       <c r="R5" t="n">
-        <v>6874859</v>
+        <v>6874858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129635001</v>
+        <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467127</v>
+        <v>467124</v>
       </c>
       <c r="R6" t="n">
-        <v>6874858</v>
+        <v>6874859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79634</v>
+        <v>78710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B18" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>78828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>79634</v>
+        <v>78827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R17" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R18" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B20" t="n">
-        <v>78710</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>78833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R13" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B14" t="n">
-        <v>78828</v>
+        <v>78741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R14" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R15" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R16" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78741</v>
+        <v>92870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>78742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>78742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R13" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78741</v>
+        <v>78834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R14" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B16" t="n">
         <v>78833</v>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B17" t="n">
-        <v>78832</v>
+        <v>79666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B18" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B20" t="n">
-        <v>78742</v>
+        <v>79666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B21" t="n">
-        <v>79666</v>
+        <v>78742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92870</v>
+        <v>78747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78742</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129635881</v>
+        <v>129635733</v>
       </c>
       <c r="B11" t="n">
-        <v>79695</v>
+        <v>79671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467091</v>
+        <v>467154</v>
       </c>
       <c r="R11" t="n">
-        <v>6874896</v>
+        <v>6874829</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129635733</v>
+        <v>129635881</v>
       </c>
       <c r="B12" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467154</v>
+        <v>467091</v>
       </c>
       <c r="R12" t="n">
-        <v>6874829</v>
+        <v>6874896</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R13" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B14" t="n">
-        <v>78834</v>
+        <v>78747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R14" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R15" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R16" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>79666</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R17" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>78833</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R18" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79666</v>
+        <v>78747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78742</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78747</v>
+        <v>92875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>78747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129635733</v>
+        <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467154</v>
+        <v>467091</v>
       </c>
       <c r="R11" t="n">
-        <v>6874829</v>
+        <v>6874896</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129635881</v>
+        <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467091</v>
+        <v>467154</v>
       </c>
       <c r="R12" t="n">
-        <v>6874896</v>
+        <v>6874829</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R13" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R14" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92875</v>
+        <v>78747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129635881</v>
+        <v>129635733</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467091</v>
+        <v>467154</v>
       </c>
       <c r="R11" t="n">
-        <v>6874896</v>
+        <v>6874829</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129635733</v>
+        <v>129635881</v>
       </c>
       <c r="B12" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467154</v>
+        <v>467091</v>
       </c>
       <c r="R12" t="n">
-        <v>6874829</v>
+        <v>6874896</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R17" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R18" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129635733</v>
+        <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467154</v>
+        <v>467091</v>
       </c>
       <c r="R11" t="n">
-        <v>6874829</v>
+        <v>6874896</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129635881</v>
+        <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467091</v>
+        <v>467154</v>
       </c>
       <c r="R12" t="n">
-        <v>6874896</v>
+        <v>6874829</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78747</v>
+        <v>92879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>78747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92879</v>
+        <v>78747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>92881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R13" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R14" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R15" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R16" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R17" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R18" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78747</v>
+        <v>92881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92881</v>
+        <v>78747</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129635001</v>
+        <v>129634992</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467127</v>
+        <v>467124</v>
       </c>
       <c r="R5" t="n">
-        <v>6874858</v>
+        <v>6874859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129634992</v>
+        <v>129635001</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467124</v>
+        <v>467127</v>
       </c>
       <c r="R6" t="n">
-        <v>6874859</v>
+        <v>6874858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92881</v>
+        <v>78747</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>92881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129635736</v>
+        <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467160</v>
+        <v>466957</v>
       </c>
       <c r="R13" t="n">
-        <v>6874835</v>
+        <v>6875023</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129637051</v>
+        <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466957</v>
+        <v>467160</v>
       </c>
       <c r="R14" t="n">
-        <v>6875023</v>
+        <v>6874835</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R15" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R16" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129634992</v>
+        <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467124</v>
+        <v>467127</v>
       </c>
       <c r="R5" t="n">
-        <v>6874859</v>
+        <v>6874858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129635001</v>
+        <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>79671</v>
+        <v>78842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467127</v>
+        <v>467124</v>
       </c>
       <c r="R6" t="n">
-        <v>6874858</v>
+        <v>6874859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78747</v>
+        <v>92884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92881</v>
+        <v>78750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B20" t="n">
-        <v>78750</v>
+        <v>79674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B21" t="n">
-        <v>79674</v>
+        <v>78750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>129635001</v>
       </c>
       <c r="B5" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>129634992</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,62 +1289,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B8" t="n">
-        <v>92884</v>
+        <v>78753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R8" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,48 +1386,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B9" t="n">
-        <v>78750</v>
+        <v>92887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129634638</v>
+        <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467109</v>
+        <v>467000</v>
       </c>
       <c r="R15" t="n">
-        <v>6874851</v>
+        <v>6874978</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R16" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79674</v>
+        <v>78753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78750</v>
+        <v>79677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B18" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B20" t="n">
-        <v>78753</v>
+        <v>79677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B21" t="n">
-        <v>79677</v>
+        <v>78753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129637210</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129635001</v>
+        <v>129634992</v>
       </c>
       <c r="B5" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467127</v>
+        <v>467124</v>
       </c>
       <c r="R5" t="n">
-        <v>6874858</v>
+        <v>6874859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129634992</v>
+        <v>129635001</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467124</v>
+        <v>467127</v>
       </c>
       <c r="R6" t="n">
-        <v>6874859</v>
+        <v>6874858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>129635902</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,48 +1289,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129637076</v>
+        <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>78753</v>
+        <v>92888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466947</v>
+        <v>466993</v>
       </c>
       <c r="R8" t="n">
-        <v>6875014</v>
+        <v>6874968</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,62 +1400,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129636078</v>
+        <v>129637076</v>
       </c>
       <c r="B9" t="n">
-        <v>92887</v>
+        <v>78754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466993</v>
+        <v>466947</v>
       </c>
       <c r="R9" t="n">
-        <v>6874968</v>
+        <v>6875014</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129634476</v>
       </c>
       <c r="B10" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129635881</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129635733</v>
       </c>
       <c r="B12" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>129637051</v>
       </c>
       <c r="B13" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>129635736</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>129636144</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>129634638</v>
       </c>
       <c r="B16" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129637336</v>
+        <v>129634628</v>
       </c>
       <c r="B17" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466937</v>
+        <v>467109</v>
       </c>
       <c r="R17" t="n">
-        <v>6875120</v>
+        <v>6874851</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129634628</v>
+        <v>129637336</v>
       </c>
       <c r="B18" t="n">
-        <v>78844</v>
+        <v>79678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467109</v>
+        <v>466937</v>
       </c>
       <c r="R18" t="n">
-        <v>6874851</v>
+        <v>6875120</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2373,7 +2373,7 @@
         <v>129635730</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129637233</v>
+        <v>129635973</v>
       </c>
       <c r="B20" t="n">
-        <v>79677</v>
+        <v>78754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466914</v>
+        <v>467044</v>
       </c>
       <c r="R20" t="n">
-        <v>6875058</v>
+        <v>6874932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2564,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129635973</v>
+        <v>129637233</v>
       </c>
       <c r="B21" t="n">
-        <v>78753</v>
+        <v>79678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467044</v>
+        <v>466914</v>
       </c>
       <c r="R21" t="n">
-        <v>6874932</v>
+        <v>6875058</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>129635621</v>
       </c>
       <c r="B22" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>129635917</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129636001</v>
       </c>
       <c r="B24" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96126804</v>
+        <v>120338318</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466935.3998369084</v>
+        <v>467109</v>
       </c>
       <c r="R2" t="n">
-        <v>6875118.580737841</v>
+        <v>6874790</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,66 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96126752</v>
+        <v>129635621</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härjedalen, Hjd</t>
+          <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467027.6755137671</v>
+        <v>467134</v>
       </c>
       <c r="R3" t="n">
-        <v>6875028.902648374</v>
+        <v>6874854</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129637210</v>
+        <v>129635973</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466935</v>
+        <v>467044</v>
       </c>
       <c r="R4" t="n">
-        <v>6875038</v>
+        <v>6874932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129634992</v>
+        <v>129637051</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467124</v>
+        <v>466957</v>
       </c>
       <c r="R5" t="n">
-        <v>6874859</v>
+        <v>6875023</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129635001</v>
+        <v>129637076</v>
       </c>
       <c r="B6" t="n">
-        <v>79678</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467127</v>
+        <v>466947</v>
       </c>
       <c r="R6" t="n">
-        <v>6874858</v>
+        <v>6875014</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129635902</v>
+        <v>129636001</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,37 +1171,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467091</v>
+        <v>467033</v>
       </c>
       <c r="R7" t="n">
-        <v>6874896</v>
+        <v>6874940</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,11 +1274,11 @@
         <v>129636078</v>
       </c>
       <c r="B8" t="n">
-        <v>92888</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1400,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129637076</v>
+        <v>129634628</v>
       </c>
       <c r="B9" t="n">
-        <v>78754</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466947</v>
+        <v>467109</v>
       </c>
       <c r="R9" t="n">
-        <v>6875014</v>
+        <v>6874851</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1497,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129634476</v>
+        <v>129636144</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1490,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467118</v>
+        <v>467000</v>
       </c>
       <c r="R10" t="n">
-        <v>6874875</v>
+        <v>6874978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129635881</v>
+        <v>129635730</v>
       </c>
       <c r="B11" t="n">
-        <v>79707</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,13 +1611,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467091</v>
+        <v>467158</v>
       </c>
       <c r="R11" t="n">
-        <v>6874896</v>
+        <v>6874824</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129635733</v>
+        <v>129635881</v>
       </c>
       <c r="B12" t="n">
-        <v>79678</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,13 +1708,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467154</v>
+        <v>467091</v>
       </c>
       <c r="R12" t="n">
-        <v>6874829</v>
+        <v>6874896</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,48 +1770,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129637051</v>
+        <v>96126752</v>
       </c>
       <c r="B13" t="n">
-        <v>78754</v>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flon, Flon, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466957</v>
+        <v>467028</v>
       </c>
       <c r="R13" t="n">
-        <v>6875023</v>
+        <v>6875029</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1853,12 +1836,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1873,22 +1856,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129635736</v>
+        <v>129634476</v>
       </c>
       <c r="B14" t="n">
-        <v>78846</v>
+        <v>79085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467160</v>
+        <v>467118</v>
       </c>
       <c r="R14" t="n">
-        <v>6874835</v>
+        <v>6874875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129636144</v>
+        <v>129634638</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>79085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1976,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,13 +2000,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467000</v>
+        <v>467109</v>
       </c>
       <c r="R15" t="n">
-        <v>6874978</v>
+        <v>6874851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2079,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129634638</v>
+        <v>129634992</v>
       </c>
       <c r="B16" t="n">
-        <v>78846</v>
+        <v>79085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,13 +2097,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467109</v>
+        <v>467124</v>
       </c>
       <c r="R16" t="n">
-        <v>6874851</v>
+        <v>6874859</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129634628</v>
+        <v>129635736</v>
       </c>
       <c r="B17" t="n">
-        <v>78845</v>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2170,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,13 +2194,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467109</v>
+        <v>467160</v>
       </c>
       <c r="R17" t="n">
-        <v>6874851</v>
+        <v>6874835</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2273,10 +2256,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129637336</v>
+        <v>129635902</v>
       </c>
       <c r="B18" t="n">
-        <v>79678</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2267,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466937</v>
+        <v>467091</v>
       </c>
       <c r="R18" t="n">
-        <v>6875120</v>
+        <v>6874896</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2370,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129635730</v>
+        <v>129635917</v>
       </c>
       <c r="B19" t="n">
-        <v>79707</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,21 +2364,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467158</v>
+        <v>467081</v>
       </c>
       <c r="R19" t="n">
-        <v>6874824</v>
+        <v>6874889</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129635973</v>
+        <v>129637210</v>
       </c>
       <c r="B20" t="n">
-        <v>78754</v>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,21 +2461,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467044</v>
+        <v>466935</v>
       </c>
       <c r="R20" t="n">
-        <v>6874932</v>
+        <v>6875038</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2564,10 +2547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129637233</v>
+        <v>96126804</v>
       </c>
       <c r="B21" t="n">
-        <v>79678</v>
+        <v>79917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,19 +2576,20 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flon, Flon, Hjd</t>
+          <t>Härjedalen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466914</v>
+        <v>466935</v>
       </c>
       <c r="R21" t="n">
-        <v>6875058</v>
+        <v>6875119</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2629,12 +2613,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2649,22 +2633,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129635621</v>
+        <v>129635001</v>
       </c>
       <c r="B22" t="n">
-        <v>78754</v>
+        <v>79917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2672,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2696,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467134</v>
+        <v>467127</v>
       </c>
       <c r="R22" t="n">
-        <v>6874854</v>
+        <v>6874858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129635917</v>
+        <v>129635733</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>79917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2769,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2793,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467081</v>
+        <v>467154</v>
       </c>
       <c r="R23" t="n">
-        <v>6874889</v>
+        <v>6874829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,59 +2839,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129636001</v>
+        <v>129637233</v>
       </c>
       <c r="B24" t="n">
-        <v>92888</v>
+        <v>79917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flon, Flon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467033</v>
+        <v>466914</v>
       </c>
       <c r="R24" t="n">
-        <v>6874940</v>
+        <v>6875058</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,6 +2933,103 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129637336</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flon, Flon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>466937</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6875120</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42999-2025 artfynd.xlsx
+++ b/artfynd/A 42999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120338318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129636001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129634628</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635730</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635881</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129634476</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129634638</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129634992</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635736</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635902</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635917</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129637051</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129637076</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129636078</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129636144</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2641,6 +2741,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96126752</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2738,6 +2843,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129637210</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96126804</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2933,6 +3048,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129637233</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,8 +3150,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129637336</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>